--- a/03-financial-report-Expense_Report_Sample.xlsx
+++ b/03-financial-report-Expense_Report_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Codex-Utopia\PROJECTS\competition-operations\WORK\CURRENT\portfolio-quality-20261019\documents\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9715AF3-AD78-43BE-BD39-8C0BF796C2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81BD00B-F136-4581-9991-570A21A7DE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="345" windowWidth="28140" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,11 +378,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_);\(#,##0.00\);&quot;-&quot;_)"/>
     <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
-    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%_);\(0.0%\);&quot;-&quot;_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,42 +392,46 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF13201B"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF5D6F66"/>
-      <name val="Arial"/>
+      <color rgb="FF5F6368"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF13201B"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF1F2328"/>
+      <name val="Georgia"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF1F2328"/>
+      <name val="Georgia"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF13201B"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF13201B"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF7D4E6B"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -439,12 +443,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E3B2B"/>
+        <fgColor rgb="FF2E3238"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF1EC"/>
+        <fgColor rgb="FFF3ECF1"/>
       </patternFill>
     </fill>
   </fills>
@@ -461,7 +465,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFDFE3DC"/>
+        <color rgb="FFDCDDE0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -469,10 +473,10 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF13201B"/>
+        <color rgb="FF1F2328"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFDFE3DC"/>
+        <color rgb="FFDCDDE0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,10 +484,10 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF13201B"/>
+        <color rgb="FF7D4E6B"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF13201B"/>
+        <color rgb="FF7D4E6B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,11 +532,11 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -556,41 +560,47 @@
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFB4412F"/>
-        <name val="Arial"/>
+        <name val="Calibri"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFB4412F"/>
-        <name val="Arial"/>
+        <name val="Calibri"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFB4412F"/>
-        <name val="Arial"/>
+        <name val="Calibri"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
-        <color rgb="FF175841"/>
-        <name val="Arial"/>
+        <sz val="11"/>
+        <color rgb="FF7D4E6B"/>
+        <name val="Calibri"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3ECF1"/>
+          <bgColor rgb="FFF3ECF1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFB4412F"/>
-        <name val="Arial"/>
+        <name val="Calibri"/>
       </font>
     </dxf>
   </dxfs>
@@ -636,11 +646,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="175841"/>
+              <a:srgbClr val="7D4E6B"/>
             </a:solidFill>
             <a:ln>
               <a:solidFill>
-                <a:srgbClr val="175841"/>
+                <a:srgbClr val="7D4E6B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -677,7 +687,7 @@
             <c:numRef>
               <c:f>Summary!$B$14:$B$19</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>#,##0.00_);\(#,##0.00\);"-"_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1678.69</c:v>
@@ -709,7 +719,7 @@
                   </a:solidFill>
                   <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="175841"/>
+                      <a:srgbClr val="7D4E6B"/>
                     </a:solidFill>
                     <a:prstDash val="solid"/>
                   </a:ln>
@@ -717,7 +727,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BD46-433C-94EA-C16EEFAB09C4}"/>
+              <c16:uniqueId val="{00000000-93E3-4596-82C9-F3C2551DCA16}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -737,11 +747,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="93B3A0"/>
+              <a:srgbClr val="BFC3C8"/>
             </a:solidFill>
             <a:ln>
               <a:solidFill>
-                <a:srgbClr val="93B3A0"/>
+                <a:srgbClr val="BFC3C8"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -778,7 +788,7 @@
             <c:numRef>
               <c:f>Summary!$C$14:$C$19</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>#,##0.00_);\(#,##0.00\);"-"_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>2100</c:v>
@@ -810,7 +820,7 @@
                   </a:solidFill>
                   <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="93B3A0"/>
+                      <a:srgbClr val="BFC3C8"/>
                     </a:solidFill>
                     <a:prstDash val="solid"/>
                   </a:ln>
@@ -818,7 +828,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BD46-433C-94EA-C16EEFAB09C4}"/>
+              <c16:uniqueId val="{00000001-93E3-4596-82C9-F3C2551DCA16}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -863,7 +873,7 @@
           <c:spPr>
             <a:ln>
               <a:solidFill>
-                <a:srgbClr val="DFE3DC"/>
+                <a:srgbClr val="DCDDE0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,7 +1264,7 @@
     <col min="7" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1327,7 +1337,7 @@
         <v>1832.4733333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>9</v>
       </c>
@@ -1504,7 +1514,7 @@
         <v>0.87260634920634916</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>16</v>
       </c>
@@ -1635,7 +1645,7 @@
         <v>0.87260634920634916</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>18</v>
       </c>
@@ -1667,7 +1677,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>22</v>
       </c>
